--- a/焊缝统计R3_auto(1).xlsx
+++ b/焊缝统计R3_auto(1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hanf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C94A95A-3A27-4062-AC36-4783E21CACAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D53757-75BF-45E5-A35F-1B42DF694732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="380" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="焊缝统计" sheetId="1" r:id="rId1"/>
@@ -3017,7 +3017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>103</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>104</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>105</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>106</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>107</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>108</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>111</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>112</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>113</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>114</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>115</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>116</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>119</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>120</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>121</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>122</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>101</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>102</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>109</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>110</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>117</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>118</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>145</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>146</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>141</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>142</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>143</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>144</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>135</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>136</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>137</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>138</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>139</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>140</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>171</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>172</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>173</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>174</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>175</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>176</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>177</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>178</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>179</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>180</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>181</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
         <v>182</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <v>165</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>166</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>167</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <v>168</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>169</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <v>170</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <v>147</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>148</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <v>149</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>150</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
         <v>151</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>152</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>153</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>154</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>155</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>156</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="5">
         <v>157</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="5">
         <v>158</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="5">
         <v>159</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="5">
         <v>160</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="5">
         <v>161</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="5">
         <v>162</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="5">
         <v>163</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="5">
         <v>164</v>
       </c>
@@ -5917,22 +5917,22 @@
     </row>
     <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C226" s="5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D226" s="5">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H226" s="5" t="s">
         <v>40</v>
@@ -5940,22 +5940,22 @@
     </row>
     <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="5">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C227" s="5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D227" s="5">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="F227" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H227" s="5" t="s">
         <v>40</v>
@@ -5963,22 +5963,22 @@
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C228" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D228" s="5">
-        <v>308</v>
+        <v>165</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G228" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H228" s="5" t="s">
         <v>40</v>
@@ -5986,22 +5986,22 @@
     </row>
     <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C229" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D229" s="5">
-        <v>308</v>
+        <v>165</v>
       </c>
       <c r="F229" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H229" s="5" t="s">
         <v>40</v>
@@ -6009,22 +6009,22 @@
     </row>
     <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C230" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D230" s="5">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="F230" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H230" s="5" t="s">
         <v>40</v>
@@ -6032,22 +6032,22 @@
     </row>
     <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C231" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D231" s="5">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="F231" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H231" s="5" t="s">
         <v>40</v>
@@ -6055,22 +6055,22 @@
     </row>
     <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C232" s="5">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D232" s="5">
-        <v>400</v>
+        <v>38</v>
       </c>
       <c r="F232" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H232" s="5" t="s">
         <v>40</v>
@@ -6078,22 +6078,22 @@
     </row>
     <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="5">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C233" s="5">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D233" s="5">
-        <v>400</v>
+        <v>38</v>
       </c>
       <c r="F233" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H233" s="5" t="s">
         <v>40</v>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="5">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>8</v>
@@ -6110,10 +6110,10 @@
         <v>16</v>
       </c>
       <c r="D234" s="5">
-        <v>157.5</v>
+        <v>405</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>41</v>
@@ -6124,7 +6124,7 @@
     </row>
     <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="5">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>11</v>
@@ -6133,10 +6133,10 @@
         <v>16</v>
       </c>
       <c r="D235" s="5">
-        <v>157.5</v>
+        <v>405</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G235" s="5" t="s">
         <v>41</v>
@@ -6147,7 +6147,7 @@
     </row>
     <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>8</v>
@@ -6156,10 +6156,10 @@
         <v>16</v>
       </c>
       <c r="D236" s="5">
-        <v>157.5</v>
+        <v>308</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G236" s="5" t="s">
         <v>41</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>11</v>
@@ -6179,10 +6179,10 @@
         <v>16</v>
       </c>
       <c r="D237" s="5">
-        <v>157.5</v>
+        <v>308</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G237" s="5" t="s">
         <v>41</v>
@@ -6193,7 +6193,7 @@
     </row>
     <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="5">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>8</v>
@@ -6202,13 +6202,13 @@
         <v>16</v>
       </c>
       <c r="D238" s="5">
-        <v>120</v>
+        <v>405</v>
       </c>
       <c r="F238" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H238" s="5" t="s">
         <v>40</v>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="5">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>11</v>
@@ -6225,13 +6225,13 @@
         <v>16</v>
       </c>
       <c r="D239" s="5">
-        <v>120</v>
+        <v>405</v>
       </c>
       <c r="F239" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H239" s="5" t="s">
         <v>40</v>
@@ -6239,22 +6239,22 @@
     </row>
     <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="5">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C240" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D240" s="5">
-        <v>120</v>
+        <v>197</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H240" s="5" t="s">
         <v>40</v>
@@ -6262,22 +6262,22 @@
     </row>
     <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="5">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C241" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D241" s="5">
-        <v>120</v>
+        <v>197</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H241" s="5" t="s">
         <v>40</v>
@@ -6285,22 +6285,22 @@
     </row>
     <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="5">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C242" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D242" s="5">
-        <v>38</v>
+        <v>197</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>40</v>
@@ -6308,22 +6308,22 @@
     </row>
     <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="5">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C243" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D243" s="5">
-        <v>38</v>
+        <v>197</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>40</v>
@@ -6331,22 +6331,22 @@
     </row>
     <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="5">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C244" s="5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D244" s="5">
-        <v>343</v>
+        <v>157.5</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H244" s="5" t="s">
         <v>40</v>
@@ -6354,22 +6354,22 @@
     </row>
     <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="5">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C245" s="5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D245" s="5">
-        <v>343</v>
+        <v>157.5</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H245" s="5" t="s">
         <v>40</v>
@@ -6377,22 +6377,22 @@
     </row>
     <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="5">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C246" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D246" s="5">
-        <v>197</v>
+        <v>157.5</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H246" s="5" t="s">
         <v>40</v>
@@ -6400,22 +6400,22 @@
     </row>
     <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="5">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C247" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D247" s="5">
-        <v>197</v>
+        <v>157.5</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H247" s="5" t="s">
         <v>40</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="5">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C248" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D248" s="5">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H248" s="5" t="s">
         <v>40</v>
@@ -6446,22 +6446,22 @@
     </row>
     <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="5">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C249" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D249" s="5">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H249" s="5" t="s">
         <v>40</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C250" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D250" s="5">
-        <v>197</v>
+        <v>120</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H250" s="5" t="s">
         <v>40</v>
@@ -6492,22 +6492,22 @@
     </row>
     <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C251" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D251" s="5">
-        <v>197</v>
+        <v>120</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H251" s="5" t="s">
         <v>40</v>
@@ -6515,22 +6515,22 @@
     </row>
     <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C252" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D252" s="5">
-        <v>165</v>
+        <v>400</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H252" s="5" t="s">
         <v>40</v>
@@ -6538,22 +6538,22 @@
     </row>
     <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C253" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D253" s="5">
-        <v>165</v>
+        <v>400</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G253" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H253" s="5" t="s">
         <v>40</v>
@@ -10381,11 +10381,11 @@
   <autoFilter ref="A1:I419" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="7">
       <filters>
-        <filter val="BE023"/>
+        <filter val="CO007"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A136:I183">
-      <sortCondition ref="G1:G419"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A226:I253">
+      <sortCondition ref="F1:F419"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/焊缝统计R3_auto(1).xlsx
+++ b/焊缝统计R3_auto(1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hanf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D53757-75BF-45E5-A35F-1B42DF694732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9104952-95CB-4D48-87A0-4E67C282D1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3300" yWindow="1920" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="焊缝统计" sheetId="1" r:id="rId1"/>
@@ -723,17 +723,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J419"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="14" style="5" customWidth="1"/>
-    <col min="3" max="3" width="23.90625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="23.875" style="5" customWidth="1"/>
     <col min="4" max="8" width="14" style="5" customWidth="1"/>
-    <col min="9" max="9" width="23.7265625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="23.75" style="5" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="5" customWidth="1"/>
     <col min="11" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -763,7 +763,7 @@
       </c>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -786,7 +786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -809,7 +809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -832,7 +832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -878,7 +878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -901,7 +901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -924,7 +924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -947,7 +947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -970,7 +970,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -993,7 +993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -2051,9 +2051,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A58" s="5">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>8</v>
@@ -2062,21 +2062,21 @@
         <v>8</v>
       </c>
       <c r="D58" s="5">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A59" s="5">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
@@ -2085,33 +2085,33 @@
         <v>8</v>
       </c>
       <c r="D59" s="5">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A60" s="5">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D60" s="5">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>19</v>
@@ -2120,21 +2120,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A61" s="5">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D61" s="5">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>19</v>
@@ -2143,18 +2143,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A62" s="5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="5">
-        <v>6</v>
-      </c>
       <c r="D62" s="5">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>18</v>
@@ -2165,19 +2162,22 @@
       <c r="H62" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I62" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A63" s="5">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D63" s="5">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>18</v>
@@ -2189,12 +2189,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A64" s="5">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>8</v>
+      </c>
+      <c r="C64" s="5">
+        <v>12</v>
       </c>
       <c r="D64" s="5">
         <v>250</v>
@@ -2208,13 +2211,10 @@
       <c r="H64" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I64" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="5">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
@@ -2235,21 +2235,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="5">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D66" s="5">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>19</v>
@@ -2258,21 +2258,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="5">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D67" s="5">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>19</v>
@@ -2281,9 +2281,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="5">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>8</v>
@@ -2304,9 +2304,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="5">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
@@ -2327,9 +2327,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="5">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>8</v>
@@ -2338,21 +2338,21 @@
         <v>8</v>
       </c>
       <c r="D70" s="5">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="5">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
@@ -2361,19 +2361,19 @@
         <v>8</v>
       </c>
       <c r="D71" s="5">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A72" s="5">
         <v>85</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A73" s="5">
         <v>86</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A74" s="5">
         <v>87</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A75" s="5">
         <v>88</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A76" s="5">
         <v>97</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A77" s="5">
         <v>98</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A78" s="5">
         <v>99</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A79" s="5">
         <v>100</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A80" s="5">
         <v>83</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A81" s="5">
         <v>84</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A82" s="5">
         <v>95</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A83" s="5">
         <v>96</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A84" s="5">
         <v>71</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A85" s="5">
         <v>72</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A86" s="5">
         <v>73</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A87" s="5">
         <v>74</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A88" s="5">
         <v>75</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A89" s="5">
         <v>76</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A90" s="5">
         <v>77</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A91" s="5">
         <v>78</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A92" s="5">
         <v>79</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A93" s="5">
         <v>80</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A94" s="5">
         <v>89</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A95" s="5">
         <v>90</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A96" s="5">
         <v>91</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A97" s="5">
         <v>92</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A98" s="5">
         <v>93</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A99" s="5">
         <v>94</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A100" s="5">
         <v>103</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="5">
         <v>104</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A102" s="5">
         <v>105</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A103" s="5">
         <v>106</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A104" s="5">
         <v>107</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A105" s="5">
         <v>108</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A106" s="5">
         <v>111</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A107" s="5">
         <v>112</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A108" s="5">
         <v>113</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A109" s="5">
         <v>114</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A110" s="5">
         <v>115</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A111" s="5">
         <v>116</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A112" s="5">
         <v>81</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A113" s="5">
         <v>82</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A114" s="5">
         <v>119</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A115" s="5">
         <v>120</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A116" s="5">
         <v>121</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A117" s="5">
         <v>122</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A118" s="5">
         <v>101</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A119" s="5">
         <v>102</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A120" s="5">
         <v>109</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A121" s="5">
         <v>110</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A122" s="5">
         <v>117</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A123" s="5">
         <v>118</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A136" s="5">
         <v>145</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A137" s="5">
         <v>146</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A138" s="5">
         <v>141</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A139" s="5">
         <v>142</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A140" s="5">
         <v>143</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A141" s="5">
         <v>144</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A142" s="5">
         <v>135</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A143" s="5">
         <v>136</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A144" s="5">
         <v>137</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A145" s="5">
         <v>138</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A146" s="5">
         <v>139</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A147" s="5">
         <v>140</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A148" s="5">
         <v>171</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A149" s="5">
         <v>172</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A150" s="5">
         <v>173</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="5">
         <v>174</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="5">
         <v>175</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A153" s="5">
         <v>176</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A154" s="5">
         <v>177</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A155" s="5">
         <v>178</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A156" s="5">
         <v>179</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="5">
         <v>180</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="5">
         <v>181</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A159" s="5">
         <v>182</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A160" s="5">
         <v>165</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A161" s="5">
         <v>166</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A162" s="5">
         <v>167</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A163" s="5">
         <v>168</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A164" s="5">
         <v>169</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A165" s="5">
         <v>170</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A166" s="5">
         <v>147</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A167" s="5">
         <v>148</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A168" s="5">
         <v>149</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A169" s="5">
         <v>150</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A170" s="5">
         <v>151</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A171" s="5">
         <v>152</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A172" s="5">
         <v>153</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A173" s="5">
         <v>154</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A174" s="5">
         <v>155</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A175" s="5">
         <v>156</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A176" s="5">
         <v>157</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A177" s="5">
         <v>158</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A178" s="5">
         <v>159</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A179" s="5">
         <v>160</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A180" s="5">
         <v>161</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A181" s="5">
         <v>162</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A182" s="5">
         <v>163</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A183" s="5">
         <v>164</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A184" s="5">
         <v>183</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A185" s="5">
         <v>184</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A186" s="5">
         <v>185</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A187" s="5">
         <v>186</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A188" s="5">
         <v>187</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A189" s="5">
         <v>188</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A190" s="5">
         <v>189</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A191" s="5">
         <v>190</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A192" s="5">
         <v>191</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="5">
         <v>192</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="5">
         <v>193</v>
       </c>
@@ -5202,7 +5202,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A195" s="5">
         <v>194</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A196" s="5">
         <v>195</v>
       </c>
@@ -5248,7 +5248,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A197" s="5">
         <v>196</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A198" s="5">
         <v>197</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="5">
         <v>198</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="5">
         <v>199</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A201" s="5">
         <v>200</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A202" s="5">
         <v>201</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A203" s="5">
         <v>202</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A204" s="5">
         <v>203</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A205" s="5">
         <v>204</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A206" s="5">
         <v>205</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A207" s="5">
         <v>206</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A208" s="5">
         <v>207</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A209" s="5">
         <v>208</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A210" s="5">
         <v>209</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A211" s="5">
         <v>210</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A212" s="5">
         <v>211</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A213" s="5">
         <v>212</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A214" s="5">
         <v>213</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A215" s="5">
         <v>214</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A216" s="5">
         <v>215</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A217" s="5">
         <v>216</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A218" s="5">
         <v>217</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A219" s="5">
         <v>218</v>
       </c>
@@ -5777,7 +5777,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A220" s="5">
         <v>219</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A221" s="5">
         <v>220</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A222" s="5">
         <v>221</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A223" s="5">
         <v>222</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A225" s="5">
         <v>224</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A226" s="5">
         <v>243</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A227" s="5">
         <v>244</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A228" s="5">
         <v>247</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A229" s="5">
         <v>248</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A230" s="5">
         <v>251</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A231" s="5">
         <v>252</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A232" s="5">
         <v>241</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A233" s="5">
         <v>242</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A234" s="5">
         <v>225</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A235" s="5">
         <v>226</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A236" s="5">
         <v>227</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A237" s="5">
         <v>228</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A238" s="5">
         <v>229</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A239" s="5">
         <v>230</v>
       </c>
@@ -6237,7 +6237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A240" s="5">
         <v>245</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A241" s="5">
         <v>246</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A242" s="5">
         <v>249</v>
       </c>
@@ -6306,7 +6306,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A243" s="5">
         <v>250</v>
       </c>
@@ -6329,7 +6329,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A244" s="5">
         <v>233</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A245" s="5">
         <v>234</v>
       </c>
@@ -6375,7 +6375,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A246" s="5">
         <v>235</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A247" s="5">
         <v>236</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A248" s="5">
         <v>237</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A249" s="5">
         <v>238</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A250" s="5">
         <v>239</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A251" s="5">
         <v>240</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A252" s="5">
         <v>231</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A253" s="5">
         <v>232</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A254" s="5">
         <v>253</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A255" s="5">
         <v>254</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A256" s="5">
         <v>255</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A257" s="5">
         <v>256</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A258" s="5">
         <v>257</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A259" s="5">
         <v>258</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A260" s="5">
         <v>259</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A261" s="5">
         <v>260</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A262" s="5">
         <v>261</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A263" s="5">
         <v>262</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A264" s="5">
         <v>263</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A265" s="5">
         <v>264</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A266" s="5">
         <v>265</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A267" s="5">
         <v>266</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A268" s="5">
         <v>267</v>
       </c>
@@ -6904,7 +6904,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A269" s="5">
         <v>268</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A270" s="5">
         <v>269</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A271" s="5">
         <v>270</v>
       </c>
@@ -6973,7 +6973,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A272" s="5">
         <v>271</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A273" s="5">
         <v>272</v>
       </c>
@@ -7019,7 +7019,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A274" s="5">
         <v>273</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A275" s="5">
         <v>274</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A276" s="5">
         <v>275</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A277" s="5">
         <v>276</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A278" s="5">
         <v>277</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A279" s="5">
         <v>278</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A280" s="5">
         <v>279</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A281" s="5">
         <v>280</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A282" s="5">
         <v>281</v>
       </c>
@@ -7226,7 +7226,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A283" s="5">
         <v>282</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A284" s="5">
         <v>283</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A285" s="5">
         <v>284</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A286" s="5">
         <v>285</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A287" s="5">
         <v>286</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A288" s="5">
         <v>287</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A289" s="5">
         <v>288</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A290" s="5">
         <v>289</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A291" s="5">
         <v>290</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A292" s="5">
         <v>291</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A293" s="5">
         <v>292</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A294" s="5">
         <v>293</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A295" s="5">
         <v>294</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A296" s="5">
         <v>295</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A297" s="5">
         <v>296</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A298" s="5">
         <v>297</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A299" s="5">
         <v>298</v>
       </c>
@@ -7617,7 +7617,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A300" s="5">
         <v>299</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A301" s="5">
         <v>300</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A302" s="5">
         <v>301</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A303" s="5">
         <v>302</v>
       </c>
@@ -7709,7 +7709,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A304" s="5">
         <v>303</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A305" s="5">
         <v>304</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A306" s="5">
         <v>305</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A307" s="5">
         <v>306</v>
       </c>
@@ -7801,7 +7801,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A308" s="5">
         <v>307</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A309" s="5">
         <v>308</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A310" s="5">
         <v>309</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A311" s="5">
         <v>310</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A312" s="5">
         <v>311</v>
       </c>
@@ -7916,7 +7916,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A313" s="5">
         <v>312</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A314" s="5">
         <v>313</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A315" s="5">
         <v>314</v>
       </c>
@@ -7985,7 +7985,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A316" s="5">
         <v>315</v>
       </c>
@@ -8008,7 +8008,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A317" s="5">
         <v>316</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A318" s="5">
         <v>317</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A319" s="5">
         <v>318</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A320" s="5">
         <v>319</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A321" s="5">
         <v>320</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A322" s="5">
         <v>321</v>
       </c>
@@ -8146,7 +8146,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A323" s="5">
         <v>322</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A324" s="5">
         <v>323</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A325" s="5">
         <v>324</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A326" s="5">
         <v>325</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A327" s="5">
         <v>326</v>
       </c>
@@ -8261,7 +8261,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A328" s="5">
         <v>327</v>
       </c>
@@ -8284,7 +8284,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A329" s="5">
         <v>328</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A330" s="5">
         <v>329</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A331" s="5">
         <v>330</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A332" s="5">
         <v>331</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A333" s="5">
         <v>332</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A334" s="5">
         <v>333</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A335" s="5">
         <v>334</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A336" s="5">
         <v>335</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A337" s="5">
         <v>336</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A338" s="5">
         <v>337</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A339" s="5">
         <v>338</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A340" s="5">
         <v>339</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A341" s="5">
         <v>340</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A342" s="5">
         <v>341</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A343" s="5">
         <v>342</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A344" s="5">
         <v>343</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A345" s="5">
         <v>344</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A346" s="5">
         <v>345</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A347" s="5">
         <v>346</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A348" s="5">
         <v>347</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A349" s="5">
         <v>348</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A350" s="5">
         <v>349</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A351" s="5">
         <v>350</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A352" s="5">
         <v>351</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A353" s="5">
         <v>352</v>
       </c>
@@ -8859,7 +8859,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A354" s="5">
         <v>353</v>
       </c>
@@ -8882,7 +8882,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A355" s="5">
         <v>354</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A356" s="5">
         <v>355</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A357" s="5">
         <v>356</v>
       </c>
@@ -8951,7 +8951,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A358" s="5">
         <v>357</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A359" s="5">
         <v>358</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A360" s="5">
         <v>359</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A361" s="5">
         <v>360</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A362" s="5">
         <v>361</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A363" s="5">
         <v>362</v>
       </c>
@@ -9089,7 +9089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A364" s="5">
         <v>363</v>
       </c>
@@ -9112,7 +9112,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A365" s="5">
         <v>364</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A366" s="5">
         <v>365</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A367" s="5">
         <v>366</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A368" s="5">
         <v>367</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A369" s="5">
         <v>368</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A370" s="5">
         <v>369</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A371" s="5">
         <v>370</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A372" s="5">
         <v>371</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A373" s="5">
         <v>372</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A374" s="5">
         <v>373</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A375" s="5">
         <v>374</v>
       </c>
@@ -9365,7 +9365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A376" s="5">
         <v>375</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A377" s="5">
         <v>376</v>
       </c>
@@ -9411,7 +9411,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A378" s="5">
         <v>377</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A379" s="5">
         <v>378</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A380" s="5">
         <v>379</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A381" s="5">
         <v>380</v>
       </c>
@@ -9503,7 +9503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A382" s="5">
         <v>381</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A383" s="5">
         <v>382</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A384" s="5">
         <v>383</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A385" s="5">
         <v>384</v>
       </c>
@@ -9595,7 +9595,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A386" s="5">
         <v>385</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A387" s="5">
         <v>386</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A388" s="5">
         <v>387</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A389" s="5">
         <v>388</v>
       </c>
@@ -9687,7 +9687,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A390" s="5">
         <v>389</v>
       </c>
@@ -9710,7 +9710,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A391" s="5">
         <v>390</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A392" s="5">
         <v>391</v>
       </c>
@@ -9756,7 +9756,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A393" s="5">
         <v>392</v>
       </c>
@@ -9779,7 +9779,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A394" s="5">
         <v>393</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A395" s="5">
         <v>394</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A396" s="5">
         <v>395</v>
       </c>
@@ -9848,7 +9848,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A397" s="5">
         <v>396</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A398" s="5">
         <v>397</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A399" s="5">
         <v>398</v>
       </c>
@@ -9917,7 +9917,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A400" s="5">
         <v>399</v>
       </c>
@@ -9940,7 +9940,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A401" s="5">
         <v>400</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A402" s="5">
         <v>401</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A403" s="5">
         <v>402</v>
       </c>
@@ -10009,7 +10009,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A404" s="5">
         <v>403</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A405" s="5">
         <v>404</v>
       </c>
@@ -10055,7 +10055,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A406" s="5">
         <v>405</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A407" s="5">
         <v>406</v>
       </c>
@@ -10101,7 +10101,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A408" s="5">
         <v>407</v>
       </c>
@@ -10124,7 +10124,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A409" s="5">
         <v>408</v>
       </c>
@@ -10147,7 +10147,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A410" s="5">
         <v>409</v>
       </c>
@@ -10170,7 +10170,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A411" s="5">
         <v>410</v>
       </c>
@@ -10193,7 +10193,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A412" s="5">
         <v>411</v>
       </c>
@@ -10216,7 +10216,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A413" s="5">
         <v>412</v>
       </c>
@@ -10239,7 +10239,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A414" s="5">
         <v>413</v>
       </c>
@@ -10262,7 +10262,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A415" s="5">
         <v>414</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A416" s="5">
         <v>415</v>
       </c>
@@ -10308,7 +10308,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A417" s="5">
         <v>416</v>
       </c>
@@ -10331,7 +10331,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A418" s="5">
         <v>417</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A419" s="5">
         <v>418</v>
       </c>
@@ -10381,11 +10381,11 @@
   <autoFilter ref="A1:I419" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="7">
       <filters>
-        <filter val="CO007"/>
+        <filter val="BE021"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A226:I253">
-      <sortCondition ref="F1:F419"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A52:I71">
+      <sortCondition ref="G1:G419"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -10397,15 +10397,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K201"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="5" max="5" width="16.90625" customWidth="1"/>
-    <col min="11" max="11" width="23.36328125" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="11" max="11" width="23.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>46</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D2">
         <v>1</v>
       </c>
@@ -10460,7 +10460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D3">
         <v>2</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D4">
         <v>3</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D5">
         <v>4</v>
       </c>
@@ -10529,7 +10529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D6">
         <v>5</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D7">
         <v>6</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D8">
         <v>7</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D9">
         <v>8</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D10">
         <v>9</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D11">
         <v>10</v>
       </c>
@@ -10667,7 +10667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D12">
         <v>11</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D13">
         <v>12</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D14">
         <v>13</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D15">
         <v>14</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D16">
         <v>15</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D17">
         <v>16</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D18">
         <v>17</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D19">
         <v>18</v>
       </c>
@@ -10851,7 +10851,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D20">
         <v>19</v>
       </c>
@@ -10874,7 +10874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D21">
         <v>20</v>
       </c>
@@ -10897,7 +10897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D22">
         <v>21</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D23">
         <v>22</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D24">
         <v>23</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D25">
         <v>24</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D26">
         <v>25</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D27">
         <v>26</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D28">
         <v>27</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D29">
         <v>28</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D30">
         <v>29</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D31">
         <v>30</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D32">
         <v>31</v>
       </c>
@@ -11150,7 +11150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D33">
         <v>32</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D34">
         <v>33</v>
       </c>
@@ -11196,7 +11196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D35">
         <v>34</v>
       </c>
@@ -11219,7 +11219,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D36">
         <v>35</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D37">
         <v>36</v>
       </c>
@@ -11265,7 +11265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D38">
         <v>37</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D39">
         <v>38</v>
       </c>
@@ -11311,7 +11311,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D40">
         <v>39</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D41">
         <v>40</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D42">
         <v>41</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D43">
         <v>42</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D44">
         <v>43</v>
       </c>
@@ -11426,7 +11426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D45">
         <v>44</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D46">
         <v>45</v>
       </c>
@@ -11472,7 +11472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D47">
         <v>46</v>
       </c>
@@ -11495,7 +11495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D48">
         <v>47</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D49">
         <v>48</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D50">
         <v>49</v>
       </c>
@@ -11564,7 +11564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D51">
         <v>50</v>
       </c>
@@ -11587,7 +11587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D52">
         <v>51</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D53">
         <v>52</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D54">
         <v>53</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D55">
         <v>54</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D56">
         <v>55</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D57">
         <v>56</v>
       </c>
@@ -11725,7 +11725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D58">
         <v>57</v>
       </c>
@@ -11748,7 +11748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D59">
         <v>58</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D60">
         <v>59</v>
       </c>
@@ -11794,7 +11794,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D61">
         <v>60</v>
       </c>
@@ -11817,7 +11817,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D62">
         <v>61</v>
       </c>
@@ -11840,7 +11840,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D63">
         <v>62</v>
       </c>
@@ -11863,7 +11863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D64">
         <v>63</v>
       </c>
@@ -11886,7 +11886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D65">
         <v>64</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D66">
         <v>65</v>
       </c>
@@ -11932,7 +11932,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D67">
         <v>66</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D68">
         <v>67</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D69">
         <v>68</v>
       </c>
@@ -12001,7 +12001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D70">
         <v>69</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D71">
         <v>70</v>
       </c>
@@ -12047,7 +12047,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D72">
         <v>71</v>
       </c>
@@ -12070,7 +12070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D73">
         <v>72</v>
       </c>
@@ -12093,7 +12093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D74">
         <v>73</v>
       </c>
@@ -12116,7 +12116,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D75">
         <v>74</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D76">
         <v>75</v>
       </c>
@@ -12162,7 +12162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D77">
         <v>76</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D78">
         <v>77</v>
       </c>
@@ -12208,7 +12208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D79">
         <v>78</v>
       </c>
@@ -12231,7 +12231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D80">
         <v>79</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D81">
         <v>80</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D82">
         <v>81</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D83">
         <v>82</v>
       </c>
@@ -12323,7 +12323,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D84">
         <v>83</v>
       </c>
@@ -12346,7 +12346,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D85">
         <v>84</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D86">
         <v>85</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D87">
         <v>86</v>
       </c>
@@ -12415,7 +12415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D88">
         <v>87</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D89">
         <v>88</v>
       </c>
@@ -12461,7 +12461,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D90">
         <v>89</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D91">
         <v>90</v>
       </c>
@@ -12507,7 +12507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D92">
         <v>91</v>
       </c>
@@ -12530,7 +12530,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D93">
         <v>92</v>
       </c>
@@ -12553,7 +12553,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D94">
         <v>93</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D95">
         <v>94</v>
       </c>
@@ -12599,7 +12599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D96">
         <v>95</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D97">
         <v>96</v>
       </c>
@@ -12645,7 +12645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D98">
         <v>97</v>
       </c>
@@ -12668,7 +12668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D99">
         <v>98</v>
       </c>
@@ -12691,7 +12691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D100">
         <v>99</v>
       </c>
@@ -12714,7 +12714,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D101">
         <v>100</v>
       </c>
@@ -12737,7 +12737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D102">
         <v>101</v>
       </c>
@@ -12760,7 +12760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D103">
         <v>102</v>
       </c>
@@ -12783,7 +12783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D104">
         <v>103</v>
       </c>
@@ -12806,7 +12806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D105">
         <v>104</v>
       </c>
@@ -12829,7 +12829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D106">
         <v>105</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D107">
         <v>106</v>
       </c>
@@ -12875,7 +12875,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D108">
         <v>107</v>
       </c>
@@ -12898,7 +12898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D109">
         <v>108</v>
       </c>
@@ -12921,7 +12921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D110">
         <v>109</v>
       </c>
@@ -12944,7 +12944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D111">
         <v>110</v>
       </c>
@@ -12967,7 +12967,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D112">
         <v>111</v>
       </c>
@@ -12990,7 +12990,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D113">
         <v>112</v>
       </c>
@@ -13013,7 +13013,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D114">
         <v>113</v>
       </c>
@@ -13036,7 +13036,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="115" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D115">
         <v>114</v>
       </c>
@@ -13059,7 +13059,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D116">
         <v>115</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D117">
         <v>116</v>
       </c>
@@ -13105,7 +13105,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D118">
         <v>117</v>
       </c>
@@ -13128,7 +13128,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D119">
         <v>118</v>
       </c>
@@ -13151,7 +13151,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D120">
         <v>119</v>
       </c>
@@ -13174,7 +13174,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D121">
         <v>120</v>
       </c>
@@ -13197,7 +13197,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D122">
         <v>121</v>
       </c>
@@ -13220,7 +13220,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="123" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D123">
         <v>122</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D124">
         <v>123</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D125">
         <v>124</v>
       </c>
@@ -13289,7 +13289,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="126" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D126">
         <v>125</v>
       </c>
@@ -13312,7 +13312,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D127">
         <v>126</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D128">
         <v>127</v>
       </c>
@@ -13358,7 +13358,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D129">
         <v>128</v>
       </c>
@@ -13381,7 +13381,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D130">
         <v>129</v>
       </c>
@@ -13404,7 +13404,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D131">
         <v>130</v>
       </c>
@@ -13427,7 +13427,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="132" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D132">
         <v>131</v>
       </c>
@@ -13450,7 +13450,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D133">
         <v>132</v>
       </c>
@@ -13473,7 +13473,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="134" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D134">
         <v>133</v>
       </c>
@@ -13496,7 +13496,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D135">
         <v>134</v>
       </c>
@@ -13519,7 +13519,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D136">
         <v>135</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D137">
         <v>136</v>
       </c>
@@ -13565,7 +13565,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D138">
         <v>137</v>
       </c>
@@ -13588,7 +13588,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D139">
         <v>138</v>
       </c>
@@ -13611,7 +13611,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D140">
         <v>139</v>
       </c>
@@ -13634,7 +13634,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D141">
         <v>140</v>
       </c>
@@ -13657,7 +13657,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D142">
         <v>141</v>
       </c>
@@ -13680,7 +13680,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D143">
         <v>142</v>
       </c>
@@ -13703,7 +13703,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="144" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D144">
         <v>143</v>
       </c>
@@ -13726,7 +13726,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="145" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D145">
         <v>144</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="146" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D146">
         <v>145</v>
       </c>
@@ -13772,7 +13772,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="147" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D147">
         <v>146</v>
       </c>
@@ -13795,7 +13795,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D148">
         <v>147</v>
       </c>
@@ -13818,7 +13818,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="149" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D149">
         <v>148</v>
       </c>
@@ -13841,7 +13841,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="150" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D150">
         <v>149</v>
       </c>
@@ -13864,7 +13864,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="151" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D151">
         <v>150</v>
       </c>
@@ -13887,7 +13887,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="152" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D152">
         <v>151</v>
       </c>
@@ -13910,7 +13910,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="153" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D153">
         <v>152</v>
       </c>
@@ -13933,7 +13933,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="154" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D154">
         <v>153</v>
       </c>
@@ -13956,7 +13956,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="155" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D155">
         <v>154</v>
       </c>
@@ -13979,7 +13979,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="156" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D156">
         <v>155</v>
       </c>
@@ -14002,7 +14002,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="157" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D157">
         <v>156</v>
       </c>
@@ -14025,7 +14025,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="158" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D158">
         <v>157</v>
       </c>
@@ -14048,7 +14048,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="159" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D159">
         <v>158</v>
       </c>
@@ -14071,7 +14071,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="160" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D160">
         <v>159</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="161" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D161">
         <v>160</v>
       </c>
@@ -14117,7 +14117,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="162" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D162">
         <v>161</v>
       </c>
@@ -14140,7 +14140,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="163" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D163">
         <v>162</v>
       </c>
@@ -14163,7 +14163,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="164" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D164">
         <v>163</v>
       </c>
@@ -14186,7 +14186,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="165" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D165">
         <v>164</v>
       </c>
@@ -14209,7 +14209,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="166" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D166">
         <v>165</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="167" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D167">
         <v>166</v>
       </c>
@@ -14255,7 +14255,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="168" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D168">
         <v>167</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="169" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D169">
         <v>168</v>
       </c>
@@ -14301,7 +14301,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D170">
         <v>169</v>
       </c>
@@ -14324,7 +14324,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="171" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D171">
         <v>170</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="172" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D172">
         <v>171</v>
       </c>
@@ -14370,7 +14370,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="173" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D173">
         <v>172</v>
       </c>
@@ -14393,7 +14393,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="174" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D174">
         <v>173</v>
       </c>
@@ -14416,7 +14416,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="175" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D175">
         <v>174</v>
       </c>
@@ -14439,7 +14439,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D176">
         <v>175</v>
       </c>
@@ -14462,7 +14462,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="177" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D177">
         <v>176</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D178">
         <v>177</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="179" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D179">
         <v>178</v>
       </c>
@@ -14531,7 +14531,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D180">
         <v>179</v>
       </c>
@@ -14554,7 +14554,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D181">
         <v>180</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D182">
         <v>181</v>
       </c>
@@ -14600,7 +14600,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D183">
         <v>182</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D184">
         <v>183</v>
       </c>
@@ -14646,7 +14646,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="185" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D185">
         <v>184</v>
       </c>
@@ -14669,7 +14669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="186" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D186">
         <v>185</v>
       </c>
@@ -14692,7 +14692,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="187" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D187">
         <v>186</v>
       </c>
@@ -14715,7 +14715,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D188">
         <v>187</v>
       </c>
@@ -14738,7 +14738,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D189">
         <v>188</v>
       </c>
@@ -14761,7 +14761,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="190" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D190">
         <v>189</v>
       </c>
@@ -14784,7 +14784,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="191" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D191">
         <v>190</v>
       </c>
@@ -14807,7 +14807,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="192" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D192">
         <v>191</v>
       </c>
@@ -14830,7 +14830,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.15">
       <c r="D193">
         <v>192</v>
       </c>
@@ -14853,7 +14853,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A194">
         <v>381</v>
       </c>
@@ -14876,7 +14876,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A195">
         <v>382</v>
       </c>
@@ -14899,7 +14899,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A196">
         <v>383</v>
       </c>
@@ -14922,7 +14922,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A197">
         <v>384</v>
       </c>
@@ -14945,7 +14945,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A198">
         <v>385</v>
       </c>
@@ -14968,7 +14968,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A199">
         <v>386</v>
       </c>
@@ -14991,7 +14991,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A200">
         <v>387</v>
       </c>
@@ -15014,7 +15014,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A201">
         <v>388</v>
       </c>

--- a/焊缝统计R3_auto(1).xlsx
+++ b/焊缝统计R3_auto(1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hanf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9104952-95CB-4D48-87A0-4E67C282D1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EC66D8-2652-4141-A407-ECE3D350B919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="1920" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4860" yWindow="4740" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="焊缝统计" sheetId="1" r:id="rId1"/>
@@ -1179,16 +1179,16 @@
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D20" s="5">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>14</v>
@@ -1202,16 +1202,16 @@
     </row>
     <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D21" s="5">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>14</v>
@@ -1225,16 +1225,16 @@
     </row>
     <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D22" s="5">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>14</v>
@@ -1248,16 +1248,16 @@
     </row>
     <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D23" s="5">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>14</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
@@ -1418,13 +1418,13 @@
         <v>12</v>
       </c>
       <c r="D30" s="5">
-        <v>300</v>
+        <v>445</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>16</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
@@ -1441,13 +1441,13 @@
         <v>12</v>
       </c>
       <c r="D31" s="5">
-        <v>300</v>
+        <v>445</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>16</v>
@@ -1455,22 +1455,22 @@
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D32" s="5">
-        <v>220</v>
+        <v>445</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>16</v>
@@ -1478,22 +1478,22 @@
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D33" s="5">
-        <v>220</v>
+        <v>445</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>16</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A35" s="5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>11</v>
@@ -1547,22 +1547,22 @@
     </row>
     <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A36" s="5">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D36" s="5">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>16</v>
@@ -1570,22 +1570,22 @@
     </row>
     <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A37" s="5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D37" s="5">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>16</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A38" s="5">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
@@ -1602,13 +1602,13 @@
         <v>7</v>
       </c>
       <c r="D38" s="5">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>16</v>
@@ -1616,7 +1616,7 @@
     </row>
     <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A39" s="5">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>11</v>
@@ -1625,13 +1625,13 @@
         <v>7</v>
       </c>
       <c r="D39" s="5">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>16</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A40" s="5">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>8</v>
@@ -1648,10 +1648,10 @@
         <v>7</v>
       </c>
       <c r="D40" s="5">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>13</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A41" s="5">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>11</v>
@@ -1671,10 +1671,10 @@
         <v>7</v>
       </c>
       <c r="D41" s="5">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>13</v>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A42" s="5">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>8</v>
@@ -1697,7 +1697,7 @@
         <v>140</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>13</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A43" s="5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
@@ -1720,7 +1720,7 @@
         <v>140</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>13</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A44" s="5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>8</v>
@@ -1743,7 +1743,7 @@
         <v>140</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>13</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A45" s="5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
@@ -1766,7 +1766,7 @@
         <v>140</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>13</v>
@@ -1777,7 +1777,7 @@
     </row>
     <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A46" s="5">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
@@ -1786,7 +1786,7 @@
         <v>7</v>
       </c>
       <c r="D46" s="5">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>16</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A47" s="5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
@@ -1809,7 +1809,7 @@
         <v>7</v>
       </c>
       <c r="D47" s="5">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>16</v>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" s="5">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D48" s="5">
-        <v>445</v>
+        <v>39</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>16</v>
@@ -1846,22 +1846,22 @@
     </row>
     <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A49" s="5">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D49" s="5">
-        <v>445</v>
+        <v>39</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>16</v>
@@ -1869,22 +1869,22 @@
     </row>
     <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A50" s="5">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D50" s="5">
-        <v>445</v>
+        <v>39</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>16</v>
@@ -1892,39 +1892,36 @@
     </row>
     <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A51" s="5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D51" s="5">
-        <v>445</v>
+        <v>39</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A52" s="5">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="5">
-        <v>6</v>
-      </c>
       <c r="D52" s="5">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>18</v>
@@ -1935,19 +1932,22 @@
       <c r="H52" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I52" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A53" s="5">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D53" s="5">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>18</v>
@@ -1959,12 +1959,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A54" s="5">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>8</v>
+      </c>
+      <c r="C54" s="5">
+        <v>12</v>
       </c>
       <c r="D54" s="5">
         <v>250</v>
@@ -1978,13 +1981,10 @@
       <c r="H54" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I54" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+    </row>
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A55" s="5">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
@@ -2005,15 +2005,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A56" s="5">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="C56" s="5">
-        <v>12</v>
       </c>
       <c r="D56" s="5">
         <v>250</v>
@@ -2027,10 +2024,13 @@
       <c r="H56" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I56" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A57" s="5">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
@@ -2051,21 +2051,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A58" s="5">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D58" s="5">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>19</v>
@@ -2074,21 +2074,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A59" s="5">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D59" s="5">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>19</v>
@@ -2097,9 +2097,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A60" s="5">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>8</v>
@@ -2120,9 +2120,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A61" s="5">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
@@ -2143,15 +2143,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A62" s="5">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="C62" s="5">
+        <v>6</v>
+      </c>
       <c r="D62" s="5">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>18</v>
@@ -2162,22 +2165,19 @@
       <c r="H62" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I62" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+    </row>
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A63" s="5">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D63" s="5">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>18</v>
@@ -2189,55 +2189,55 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A64" s="5">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D64" s="5">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>19</v>
+      <c r="G64" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="H64" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A65" s="5">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D65" s="5">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>19</v>
+      <c r="G65" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A66" s="5">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>8</v>
@@ -2246,21 +2246,21 @@
         <v>8</v>
       </c>
       <c r="D66" s="5">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A67" s="5">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
@@ -2269,21 +2269,21 @@
         <v>8</v>
       </c>
       <c r="D67" s="5">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="H67" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A68" s="5">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>8</v>
@@ -2292,21 +2292,21 @@
         <v>8</v>
       </c>
       <c r="D68" s="5">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A69" s="5">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
@@ -2315,21 +2315,21 @@
         <v>8</v>
       </c>
       <c r="D69" s="5">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A70" s="5">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>8</v>
@@ -2338,21 +2338,21 @@
         <v>8</v>
       </c>
       <c r="D70" s="5">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A71" s="5">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
@@ -2361,136 +2361,136 @@
         <v>8</v>
       </c>
       <c r="D71" s="5">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A72" s="5">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D72" s="5">
-        <v>140</v>
+        <v>534</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H72" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A73" s="5">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D73" s="5">
-        <v>140</v>
+        <v>534</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H73" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A74" s="5">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D74" s="5">
-        <v>29</v>
+        <v>534</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A75" s="5">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D75" s="5">
-        <v>29</v>
+        <v>534</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A76" s="5">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C76" s="5">
-        <v>7</v>
-      </c>
       <c r="D76" s="5">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H76" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+      <c r="I76" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A77" s="5">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
@@ -2499,44 +2499,44 @@
         <v>7</v>
       </c>
       <c r="D77" s="5">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A78" s="5">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C78" s="5">
-        <v>7</v>
-      </c>
       <c r="D78" s="5">
-        <v>29</v>
+        <v>270</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H78" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+      <c r="I78" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A79" s="5">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
@@ -2545,67 +2545,67 @@
         <v>7</v>
       </c>
       <c r="D79" s="5">
-        <v>29</v>
+        <v>270</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A80" s="5">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D80" s="5">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A81" s="5">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D81" s="5">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A82" s="5">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>8</v>
@@ -2617,7 +2617,7 @@
         <v>140</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>24</v>
@@ -2626,9 +2626,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A83" s="5">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
@@ -2640,7 +2640,7 @@
         <v>140</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>24</v>
@@ -2649,124 +2649,124 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A84" s="5">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D84" s="5">
-        <v>534</v>
+        <v>140</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A85" s="5">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D85" s="5">
-        <v>534</v>
+        <v>140</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A86" s="5">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D86" s="5">
-        <v>534</v>
+        <v>140</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A87" s="5">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D87" s="5">
-        <v>534</v>
+        <v>140</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H87" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A88" s="5">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>8</v>
+      </c>
+      <c r="C88" s="5">
+        <v>7</v>
       </c>
       <c r="D88" s="5">
         <v>140</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I88" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A89" s="5">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>11</v>
@@ -2778,24 +2778,24 @@
         <v>140</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H89" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A90" s="5">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="5">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>20</v>
@@ -2810,9 +2810,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A91" s="5">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>11</v>
@@ -2821,7 +2821,7 @@
         <v>7</v>
       </c>
       <c r="D91" s="5">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>20</v>
@@ -2833,7 +2833,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A92" s="5">
         <v>79</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A93" s="5">
         <v>80</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A94" s="5">
         <v>89</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A95" s="5">
         <v>90</v>
       </c>
@@ -2925,15 +2925,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A96" s="5">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="5">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>20</v>
@@ -2945,12 +2945,12 @@
         <v>20</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A97" s="5">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>11</v>
@@ -2959,7 +2959,7 @@
         <v>7</v>
       </c>
       <c r="D97" s="5">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>20</v>
@@ -2971,32 +2971,32 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A98" s="5">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="C98" s="5">
+        <v>7</v>
+      </c>
       <c r="D98" s="5">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I98" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A99" s="5">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>11</v>
@@ -3005,13 +3005,13 @@
         <v>7</v>
       </c>
       <c r="D99" s="5">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>20</v>
@@ -3019,45 +3019,45 @@
     </row>
     <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A100" s="5">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="C100" s="5">
+        <v>9</v>
+      </c>
       <c r="D100" s="5">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I100" s="5" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="101" spans="1:9" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="5">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C101" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D101" s="5">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H101" s="5" t="s">
         <v>25</v>
@@ -3111,13 +3111,13 @@
     </row>
     <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A104" s="5">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="5">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>25</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A105" s="5">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>11</v>
@@ -3143,7 +3143,7 @@
         <v>7</v>
       </c>
       <c r="D105" s="5">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>25</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A106" s="5">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>8</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A107" s="5">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>11</v>
@@ -3203,13 +3203,13 @@
     </row>
     <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A108" s="5">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="5">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>25</v>
@@ -3226,7 +3226,7 @@
     </row>
     <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A109" s="5">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>11</v>
@@ -3235,7 +3235,7 @@
         <v>7</v>
       </c>
       <c r="D109" s="5">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>25</v>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A110" s="5">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>8</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A111" s="5">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>11</v>
@@ -3293,61 +3293,58 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A112" s="5">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C112" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D112" s="5">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H112" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A113" s="5">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C113" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D113" s="5">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A114" s="5">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="C114" s="5">
-        <v>7</v>
       </c>
       <c r="D114" s="5">
         <v>140</v>
@@ -3356,15 +3353,18 @@
         <v>25</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H114" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+      <c r="I114" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A115" s="5">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>11</v>
@@ -3379,15 +3379,15 @@
         <v>25</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H115" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A116" s="5">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>8</v>
@@ -3396,7 +3396,7 @@
         <v>7</v>
       </c>
       <c r="D116" s="5">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>25</v>
@@ -3408,9 +3408,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A117" s="5">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>11</v>
@@ -3419,7 +3419,7 @@
         <v>7</v>
       </c>
       <c r="D117" s="5">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>25</v>
@@ -3431,101 +3431,101 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A118" s="5">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D118" s="5">
-        <v>440</v>
+        <v>140</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H118" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A119" s="5">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C119" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D119" s="5">
-        <v>440</v>
+        <v>140</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A120" s="5">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C120" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D120" s="5">
         <v>140</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H120" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A121" s="5">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C121" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D121" s="5">
         <v>140</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H121" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A122" s="5">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>8</v>
@@ -3534,10 +3534,10 @@
         <v>7</v>
       </c>
       <c r="D122" s="5">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G122" s="5" t="s">
         <v>28</v>
@@ -3546,9 +3546,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A123" s="5">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>11</v>
@@ -3557,10 +3557,10 @@
         <v>7</v>
       </c>
       <c r="D123" s="5">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>28</v>
@@ -3569,7 +3569,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -6055,22 +6055,22 @@
     </row>
     <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A232" s="5">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C232" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D232" s="5">
-        <v>38</v>
+        <v>197</v>
       </c>
       <c r="F232" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H232" s="5" t="s">
         <v>40</v>
@@ -6078,22 +6078,22 @@
     </row>
     <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A233" s="5">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C233" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D233" s="5">
-        <v>38</v>
+        <v>197</v>
       </c>
       <c r="F233" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H233" s="5" t="s">
         <v>40</v>
@@ -6101,22 +6101,22 @@
     </row>
     <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A234" s="5">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C234" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D234" s="5">
-        <v>405</v>
+        <v>197</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H234" s="5" t="s">
         <v>40</v>
@@ -6124,22 +6124,22 @@
     </row>
     <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A235" s="5">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C235" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D235" s="5">
-        <v>405</v>
+        <v>197</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H235" s="5" t="s">
         <v>40</v>
@@ -6147,7 +6147,7 @@
     </row>
     <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A236" s="5">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>8</v>
@@ -6156,13 +6156,13 @@
         <v>16</v>
       </c>
       <c r="D236" s="5">
-        <v>308</v>
+        <v>120</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H236" s="5" t="s">
         <v>40</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A237" s="5">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>11</v>
@@ -6179,13 +6179,13 @@
         <v>16</v>
       </c>
       <c r="D237" s="5">
-        <v>308</v>
+        <v>120</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H237" s="5" t="s">
         <v>40</v>
@@ -6193,7 +6193,7 @@
     </row>
     <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A238" s="5">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>8</v>
@@ -6202,13 +6202,13 @@
         <v>16</v>
       </c>
       <c r="D238" s="5">
-        <v>405</v>
+        <v>120</v>
       </c>
       <c r="F238" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H238" s="5" t="s">
         <v>40</v>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A239" s="5">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>11</v>
@@ -6225,13 +6225,13 @@
         <v>16</v>
       </c>
       <c r="D239" s="5">
-        <v>405</v>
+        <v>120</v>
       </c>
       <c r="F239" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H239" s="5" t="s">
         <v>40</v>
@@ -6239,22 +6239,22 @@
     </row>
     <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A240" s="5">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C240" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D240" s="5">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H240" s="5" t="s">
         <v>40</v>
@@ -6262,22 +6262,22 @@
     </row>
     <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A241" s="5">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C241" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D241" s="5">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H241" s="5" t="s">
         <v>40</v>
@@ -6285,22 +6285,22 @@
     </row>
     <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A242" s="5">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C242" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D242" s="5">
-        <v>197</v>
+        <v>405</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>40</v>
@@ -6308,22 +6308,22 @@
     </row>
     <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A243" s="5">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C243" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D243" s="5">
-        <v>197</v>
+        <v>405</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>40</v>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A244" s="5">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>8</v>
@@ -6340,10 +6340,10 @@
         <v>16</v>
       </c>
       <c r="D244" s="5">
-        <v>157.5</v>
+        <v>308</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G244" s="5" t="s">
         <v>41</v>
@@ -6354,7 +6354,7 @@
     </row>
     <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A245" s="5">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>11</v>
@@ -6363,10 +6363,10 @@
         <v>16</v>
       </c>
       <c r="D245" s="5">
-        <v>157.5</v>
+        <v>308</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G245" s="5" t="s">
         <v>41</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A246" s="5">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>8</v>
@@ -6386,13 +6386,13 @@
         <v>16</v>
       </c>
       <c r="D246" s="5">
-        <v>157.5</v>
+        <v>405</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="H246" s="5" t="s">
         <v>40</v>
@@ -6400,7 +6400,7 @@
     </row>
     <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A247" s="5">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>11</v>
@@ -6409,13 +6409,13 @@
         <v>16</v>
       </c>
       <c r="D247" s="5">
-        <v>157.5</v>
+        <v>405</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="H247" s="5" t="s">
         <v>40</v>
@@ -6423,7 +6423,7 @@
     </row>
     <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A248" s="5">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>8</v>
@@ -6432,13 +6432,13 @@
         <v>16</v>
       </c>
       <c r="D248" s="5">
-        <v>120</v>
+        <v>157.5</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H248" s="5" t="s">
         <v>40</v>
@@ -6446,7 +6446,7 @@
     </row>
     <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A249" s="5">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>11</v>
@@ -6455,13 +6455,13 @@
         <v>16</v>
       </c>
       <c r="D249" s="5">
-        <v>120</v>
+        <v>157.5</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H249" s="5" t="s">
         <v>40</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A250" s="5">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>8</v>
@@ -6478,13 +6478,13 @@
         <v>16</v>
       </c>
       <c r="D250" s="5">
-        <v>120</v>
+        <v>157.5</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H250" s="5" t="s">
         <v>40</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A251" s="5">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>11</v>
@@ -6501,13 +6501,13 @@
         <v>16</v>
       </c>
       <c r="D251" s="5">
-        <v>120</v>
+        <v>157.5</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H251" s="5" t="s">
         <v>40</v>
@@ -10381,11 +10381,11 @@
   <autoFilter ref="A1:I419" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="7">
       <filters>
-        <filter val="BE021"/>
+        <filter val="BE022"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A52:I71">
-      <sortCondition ref="G1:G419"/>
+      <sortCondition descending="1" ref="D1:D419"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/焊缝统计R3_auto(1).xlsx
+++ b/焊缝统计R3_auto(1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hanf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AD5D26-BB05-4C1B-8F60-11062E98BBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A01BC1-DF1E-452D-A690-98E5E9E0D175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12890" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="焊缝统计" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="89">
   <si>
     <t>序号</t>
   </si>
@@ -326,6 +326,10 @@
   </si>
   <si>
     <t>零件1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>p102</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4995,7 +4999,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A186" s="5">
         <v>197</v>
       </c>
@@ -5018,7 +5022,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A187" s="5">
         <v>198</v>
       </c>
@@ -5133,7 +5137,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A192" s="5">
         <v>193</v>
       </c>
@@ -5147,7 +5151,7 @@
         <v>90.5</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G192" s="5" t="s">
         <v>57</v>
@@ -5156,7 +5160,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="5">
         <v>194</v>
       </c>
@@ -5170,7 +5174,7 @@
         <v>90.5</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G193" s="5" t="s">
         <v>57</v>
@@ -5179,7 +5183,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:9" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="5">
         <v>195</v>
       </c>
@@ -5202,7 +5206,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
       <c r="A195" s="5">
         <v>196</v>
       </c>
@@ -5239,7 +5243,7 @@
         <v>90.5</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>58</v>
@@ -5262,7 +5266,7 @@
         <v>90.5</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G197" s="5" t="s">
         <v>58</v>
@@ -10379,9 +10383,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I419" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="6">
+    <filterColumn colId="5">
       <filters>
-        <filter val="p127"/>
+        <filter val="p100"/>
       </filters>
     </filterColumn>
     <filterColumn colId="7">

--- a/焊缝统计R3_auto(1).xlsx
+++ b/焊缝统计R3_auto(1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17680"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="焊缝统计" sheetId="1" r:id="rId1"/>
@@ -1386,16 +1386,16 @@
     </row>
     <row r="6" hidden="1" spans="1:8">
       <c r="A6" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D6" s="4">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>9</v>
@@ -1409,16 +1409,16 @@
     </row>
     <row r="7" hidden="1" spans="1:8">
       <c r="A7" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7" s="4">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>9</v>
@@ -1432,16 +1432,16 @@
     </row>
     <row r="8" hidden="1" spans="1:8">
       <c r="A8" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>9</v>
@@ -1455,16 +1455,16 @@
     </row>
     <row r="9" hidden="1" spans="1:8">
       <c r="A9" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D9" s="4">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>9</v>
@@ -4144,7 +4144,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:8">
+    <row r="126" spans="1:8">
       <c r="A126" s="4">
         <v>191</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:8">
+    <row r="127" spans="1:8">
       <c r="A127" s="4">
         <v>192</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:8">
+    <row r="128" spans="1:8">
       <c r="A128" s="4">
         <v>197</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:8">
+    <row r="129" spans="1:8">
       <c r="A129" s="4">
         <v>198</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="1:8">
+    <row r="142" spans="1:8">
       <c r="A142" s="4">
         <v>187</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="143" ht="12" hidden="1" customHeight="1" spans="1:8">
+    <row r="143" ht="12" customHeight="1" spans="1:8">
       <c r="A143" s="4">
         <v>188</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="144" ht="12" hidden="1" customHeight="1" spans="1:10">
+    <row r="144" ht="12" customHeight="1" spans="1:10">
       <c r="A144" s="4">
         <v>189</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="1:8">
+    <row r="145" spans="1:8">
       <c r="A145" s="4">
         <v>190</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="146" hidden="1" spans="1:8">
+    <row r="146" spans="1:8">
       <c r="A146" s="4">
         <v>193</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="147" hidden="1" spans="1:8">
+    <row r="147" spans="1:8">
       <c r="A147" s="4">
         <v>194</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="1:8">
+    <row r="148" spans="1:8">
       <c r="A148" s="4">
         <v>195</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="149" hidden="1" spans="1:8">
+    <row r="149" spans="1:8">
       <c r="A149" s="4">
         <v>196</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="1:8">
+    <row r="150" spans="1:8">
       <c r="A150" s="4">
         <v>199</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="1:8">
+    <row r="151" spans="1:8">
       <c r="A151" s="4">
         <v>200</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="160" hidden="1" spans="1:8">
+    <row r="160" spans="1:8">
       <c r="A160" s="4">
         <v>185</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="161" hidden="1" spans="1:8">
+    <row r="161" spans="1:8">
       <c r="A161" s="4">
         <v>186</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="162" hidden="1" spans="1:8">
+    <row r="162" spans="1:8">
       <c r="A162" s="4">
         <v>207</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="1:8">
+    <row r="163" spans="1:8">
       <c r="A163" s="4">
         <v>208</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="168" hidden="1" spans="1:8">
+    <row r="168" spans="1:8">
       <c r="A168" s="4">
         <v>211</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="169" hidden="1" spans="1:8">
+    <row r="169" spans="1:8">
       <c r="A169" s="4">
         <v>212</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="170" hidden="1" spans="1:8">
+    <row r="170" spans="1:8">
       <c r="A170" s="4">
         <v>191</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="171" hidden="1" spans="1:8">
+    <row r="171" spans="1:8">
       <c r="A171" s="4">
         <v>192</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="172" hidden="1" spans="1:8">
+    <row r="172" spans="1:8">
       <c r="A172" s="4">
         <v>197</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="173" hidden="1" spans="1:8">
+    <row r="173" spans="1:8">
       <c r="A173" s="4">
         <v>198</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" hidden="1" spans="1:9">
+    <row r="174" spans="1:9">
       <c r="A174" s="4">
         <v>213</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="175" hidden="1" spans="1:9">
+    <row r="175" spans="1:9">
       <c r="A175" s="4">
         <v>217</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="178" ht="12" hidden="1" customHeight="1" spans="1:9">
+    <row r="178" ht="12" customHeight="1" spans="1:9">
       <c r="A178" s="4">
         <v>219</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" hidden="1" spans="1:9">
+    <row r="179" spans="1:9">
       <c r="A179" s="4">
         <v>223</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="186" hidden="1" spans="1:8">
+    <row r="186" spans="1:8">
       <c r="A186" s="4">
         <v>203</v>
       </c>
@@ -5550,7 +5550,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="187" hidden="1" spans="1:8">
+    <row r="187" spans="1:8">
       <c r="A187" s="4">
         <v>204</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="188" hidden="1" spans="1:8">
+    <row r="188" spans="1:8">
       <c r="A188" s="4">
         <v>205</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="189" hidden="1" spans="1:8">
+    <row r="189" spans="1:8">
       <c r="A189" s="4">
         <v>206</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="190" hidden="1" spans="1:8">
+    <row r="190" spans="1:8">
       <c r="A190" s="4">
         <v>209</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="191" hidden="1" spans="1:8">
+    <row r="191" spans="1:8">
       <c r="A191" s="4">
         <v>210</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="196" hidden="1" spans="1:9">
+    <row r="196" spans="1:9">
       <c r="A196" s="4">
         <v>215</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" hidden="1" spans="1:9">
+    <row r="197" spans="1:9">
       <c r="A197" s="4">
         <v>221</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" hidden="1" spans="1:8">
+    <row r="198" spans="1:8">
       <c r="A198" s="4">
         <v>201</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="199" hidden="1" spans="1:8">
+    <row r="199" spans="1:8">
       <c r="A199" s="4">
         <v>202</v>
       </c>
@@ -5849,7 +5849,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="200" hidden="1" spans="1:8">
+    <row r="200" spans="1:8">
       <c r="A200" s="4">
         <v>205</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="201" hidden="1" spans="1:8">
+    <row r="201" spans="1:8">
       <c r="A201" s="4">
         <v>206</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="202" hidden="1" spans="1:8">
+    <row r="202" spans="1:8">
       <c r="A202" s="4">
         <v>183</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="203" ht="10" hidden="1" customHeight="1" spans="1:8">
+    <row r="203" ht="10" customHeight="1" spans="1:8">
       <c r="A203" s="4">
         <v>184</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" hidden="1" spans="1:8">
       <c r="A206" s="4">
         <v>241</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" hidden="1" spans="1:8">
       <c r="A207" s="4">
         <v>242</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" hidden="1" spans="1:8">
       <c r="A208" s="4">
         <v>237</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" hidden="1" spans="1:8">
       <c r="A209" s="4">
         <v>238</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" hidden="1" spans="1:8">
       <c r="A210" s="4">
         <v>239</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" hidden="1" spans="1:8">
       <c r="A211" s="4">
         <v>240</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" hidden="1" spans="1:8">
       <c r="A212" s="4">
         <v>233</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" hidden="1" spans="1:8">
       <c r="A213" s="4">
         <v>234</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" hidden="1" spans="1:8">
       <c r="A214" s="4">
         <v>235</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" hidden="1" spans="1:8">
       <c r="A215" s="4">
         <v>236</v>
       </c>
@@ -6217,7 +6217,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" hidden="1" spans="1:8">
       <c r="A216" s="4">
         <v>247</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" hidden="1" spans="1:8">
       <c r="A217" s="4">
         <v>248</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" hidden="1" spans="1:8">
       <c r="A218" s="4">
         <v>251</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" hidden="1" spans="1:8">
       <c r="A219" s="4">
         <v>252</v>
       </c>
@@ -6309,7 +6309,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" hidden="1" spans="1:8">
       <c r="A220" s="4">
         <v>245</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" hidden="1" spans="1:8">
       <c r="A221" s="4">
         <v>246</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" hidden="1" spans="1:8">
       <c r="A222" s="4">
         <v>249</v>
       </c>
@@ -6378,7 +6378,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" hidden="1" spans="1:8">
       <c r="A223" s="4">
         <v>250</v>
       </c>
@@ -6401,7 +6401,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" hidden="1" spans="1:8">
       <c r="A224" s="4">
         <v>227</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" hidden="1" spans="1:8">
       <c r="A225" s="4">
         <v>228</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" hidden="1" spans="1:8">
       <c r="A226" s="4">
         <v>243</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" hidden="1" spans="1:8">
       <c r="A227" s="4">
         <v>244</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" hidden="1" spans="1:8">
       <c r="A228" s="4">
         <v>231</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" hidden="1" spans="1:8">
       <c r="A229" s="4">
         <v>232</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" hidden="1" spans="1:8">
       <c r="A230" s="4">
         <v>225</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" hidden="1" spans="1:8">
       <c r="A231" s="4">
         <v>226</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" hidden="1" spans="1:8">
       <c r="A232" s="4">
         <v>229</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" hidden="1" spans="1:8">
       <c r="A233" s="4">
         <v>230</v>
       </c>
@@ -10131,11 +10131,11 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I385" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="7">
       <filters>
-        <filter val="CO009"/>
+        <filter val="CO008"/>
       </filters>
     </filterColumn>
-    <sortState ref="A1:I385">
-      <sortCondition ref="D1"/>
+    <sortState ref="A2:I385">
+      <sortCondition ref="D1" descending="1"/>
     </sortState>
     <extLst/>
   </autoFilter>
